--- a/downloads/forms/written-apology.xlsx
+++ b/downloads/forms/written-apology.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="D6" s="3" t="n"/>
     </row>
-    <row r="7" ht="198.4251968503937" customHeight="1">
+    <row r="7" ht="238.1102362204725" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>경 위</t>
@@ -650,11 +650,11 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="22.67716535433071" customHeight="1"/>
+    <row r="14" ht="17.00787401574803" customHeight="1"/>
     <row r="15" ht="20.8" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">                              귀하</t>
+          <t>______________________________  귀하</t>
         </is>
       </c>
     </row>
